--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MARYLAND_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MARYLAND_2019.xlsx
@@ -1687,7 +1687,7 @@
         <v>21</v>
       </c>
       <c r="D74">
-        <v>0.009102730819245773</v>
+        <v>0.009102730819245772</v>
       </c>
     </row>
     <row r="75">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C152">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C408">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C411">
